--- a/experiments/Experimental_results.xlsx
+++ b/experiments/Experimental_results.xlsx
@@ -2,7 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Selection" sheetId="1" r:id="Rc63692fb28904d19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Selection" sheetId="1" r:id="R45888a6049d44b4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit_App_Tests" sheetId="2" r:id="Rf3b9fcf0835e4831"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Review_Scoring" sheetId="3" r:id="R4b776c825f444c15"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -221,7 +223,7 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
+      <x:c r="A2" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="str">
@@ -233,16 +235,16 @@
       <x:c r="D2" t="str">
         <x:v>CPU</x:v>
       </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="E2" t="n">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="F2" t="n">
         <x:v>0.7033</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="G2" t="n">
         <x:v>38.6122</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H2" t="n">
         <x:v>27.8509</x:v>
       </x:c>
       <x:c r="I2" t="str">
@@ -250,7 +252,7 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
+      <x:c r="A3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" t="str">
@@ -262,16 +264,16 @@
       <x:c r="D3" t="str">
         <x:v>GPU</x:v>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E3" t="n">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="F3" t="n">
         <x:v>0.7033</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="G3" t="n">
         <x:v>4.8555</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H3" t="n">
         <x:v>3.9927</x:v>
       </x:c>
       <x:c r="I3" t="str">
@@ -279,7 +281,7 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
+      <x:c r="A4" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="str">
@@ -291,16 +293,16 @@
       <x:c r="D4" t="str">
         <x:v>CPU</x:v>
       </x:c>
-      <x:c r="E4" t="str">
+      <x:c r="E4" t="n">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F4" t="str">
+      <x:c r="F4" t="n">
         <x:v>0.7604</x:v>
       </x:c>
-      <x:c r="G4" t="str">
+      <x:c r="G4" t="n">
         <x:v>30.7984</x:v>
       </x:c>
-      <x:c r="H4" t="str">
+      <x:c r="H4" t="n">
         <x:v>25.9997</x:v>
       </x:c>
       <x:c r="I4" t="str">
@@ -308,7 +310,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
+      <x:c r="A5" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="str">
@@ -320,16 +322,16 @@
       <x:c r="D5" t="str">
         <x:v>GPU</x:v>
       </x:c>
-      <x:c r="E5" t="str">
+      <x:c r="E5" t="n">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F5" t="str">
+      <x:c r="F5" t="n">
         <x:v>0.7604</x:v>
       </x:c>
-      <x:c r="G5" t="str">
+      <x:c r="G5" t="n">
         <x:v>3.2396</x:v>
       </x:c>
-      <x:c r="H5" t="str">
+      <x:c r="H5" t="n">
         <x:v>2.2477</x:v>
       </x:c>
       <x:c r="I5" t="str">
@@ -337,7 +339,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
+      <x:c r="A6" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" t="str">
@@ -349,24 +351,24 @@
       <x:c r="D6" t="str">
         <x:v>CPU</x:v>
       </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="E6" t="n">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F6" t="str">
+      <x:c r="F6" t="n">
         <x:v>0.7363</x:v>
       </x:c>
-      <x:c r="G6" t="str">
+      <x:c r="G6" t="n">
         <x:v>57.5298</x:v>
       </x:c>
-      <x:c r="H6" t="str">
-        <x:v>50.5400</x:v>
+      <x:c r="H6" t="n">
+        <x:v>50.54</x:v>
       </x:c>
       <x:c r="I6" t="str">
         <x:v>Sentiment pipeline as supporting signal</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
+      <x:c r="A7" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" t="str">
@@ -378,20 +380,342 @@
       <x:c r="D7" t="str">
         <x:v>GPU</x:v>
       </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="E7" t="n">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F7" t="str">
+      <x:c r="F7" t="n">
         <x:v>0.7363</x:v>
       </x:c>
-      <x:c r="G7" t="str">
-        <x:v>6.1080</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
+      <x:c r="G7" t="n">
+        <x:v>6.108</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
         <x:v>4.2489</x:v>
       </x:c>
       <x:c r="I7" t="str">
         <x:v>Sentiment pipeline on GPU</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>video</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>num_comments</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>app_main_emotion</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>manual_main_emotion</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>correct</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>negative_emotion_ratio</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>anger_pct</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>disgust_pct</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>fear_pct</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>joy_pct</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>neutral_pct</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>sadness_pct</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>surprise_pct</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>https://www.youtube.com/watch?v=d2dgJGkw5p0</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K2" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>https://www.youtube.com/watch?v=M8To7iorkxQ</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>joy</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K3" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>https://www.youtube.com/watch?v=-_-eIVAX1yQ</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>anger</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K4" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>video</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>num_comments</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>manual_7_emotion</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>manual_7_score</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>app_7_emotion</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>emotion_correct</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>manual_3_sentiment</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>manual_3_score</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>app_3_sentiment</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>sentiment_correct</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>rationale</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>https://www.youtube.com/watch?v=d2dgJGkw5p0</x:v>
+      </x:c>
+      <x:c r="B2" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="H2" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>Mostly informational and geopolitical discussion; some sarcasm and criticism are present, but no single strong emotion dominates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>https://www.youtube.com/watch?v=M8To7iorkxQ</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>joy</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>positive</x:v>
+      </x:c>
+      <x:c r="H3" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>positive</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>Many comments praise the video or movie, use hearts, and contain positive wording such as amazing, enjoying, and favorite.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>https://www.youtube.com/watch?v=-_-eIVAX1yQ</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>anger</x:v>
+      </x:c>
+      <x:c r="D4" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>negative</x:v>
+      </x:c>
+      <x:c r="H4" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>negative</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>Comments include blame, insults, political hostility, and violent sarcasm; negative anger dominates despite some dark humor.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/experiments/Experimental_results.xlsx
+++ b/experiments/Experimental_results.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Selection" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit_App_Performance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Runtime" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Comment_Labels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_5Model_Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Runtime" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Comment_Labels" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,14 +447,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="39" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,10 +814,10 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1522,239 +1523,842 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>model</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>num_comments</t>
+          <t>task</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>runtime_with_model_loading_seconds</t>
+          <t>matched</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>runtime_without_model_loading_seconds</t>
+          <t>total</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>load_s</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>infer_s</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Pre-tuning baseline</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>j-hartmann/emotion-english-distilroberta-base</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>150 reviewed Streamlit app comments</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>150</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.2815</v>
+        <v>29</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1.5164</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>pre-tuning public baseline</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>150 reviewed Streamlit app comments</t>
+          <t>Pre-tuning baseline</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>150</v>
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12.8617</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1.3363</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>GoEmotions fine-tuned DistilBERT</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>150 reviewed Streamlit app comments</t>
+          <t>Pre-tuning baseline</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>150</v>
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14.8326</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1.4346</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted DistilBERT</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SamLowe/roberta-base-go_emotions</t>
+          <t>OVERALL</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>150 reviewed Streamlit app comments</t>
+          <t>Pre-tuning baseline</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>4.8483</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.8838</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>public GoEmotions RoBERTa</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>0.4466666666666666</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-roberta-large</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>150 reviewed Streamlit app comments</t>
+          <t>GoEmotions fine-tuned</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>150</v>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>40.846</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>11.9566</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>public RoBERTa-large seven-emotion</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>GoEmotions fine-tuned</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>GoEmotions fine-tuned</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>GoEmotions fine-tuned</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted (your model)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted (your model)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted (your model)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted (your model)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.4733333333333333</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>SamLowe/roberta-base-go_emotions</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>SamLowe/roberta-base-go_emotions</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SamLowe/roberta-base-go_emotions</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>SamLowe/roberta-base-go_emotions</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0.2733333333333333</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Public RoBERTa-large 7-emotion</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-roberta-large</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Public RoBERTa-large 7-emotion</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-roberta-large</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Public RoBERTa-large 7-emotion</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-roberta-large</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Public RoBERTa-large 7-emotion</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-roberta-large</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0.4133333333333333</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>3-sentiment pipeline</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>150 reviewed Streamlit app comments</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>4.304</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>3.0499</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>supporting sentiment pipeline</t>
-        </is>
+      <c r="G22" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1768,13 +2372,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>num_comments</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>runtime_with_model_loading_seconds</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>runtime_without_model_loading_seconds</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>7.2815</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1.5164</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>pre-tuning public baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>12.8617</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1.3363</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>GoEmotions fine-tuned DistilBERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>14.8326</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1.4346</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted DistilBERT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SamLowe/roberta-base-go_emotions</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4.8483</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.8838</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>public GoEmotions RoBERTa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-roberta-large</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>40.846</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>11.9566</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>public RoBERTa-large seven-emotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4.304</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.0499</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>supporting sentiment pipeline</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>

--- a/experiments/Experimental_results.xlsx
+++ b/experiments/Experimental_results.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,10 +513,10 @@
         <v>0.6204</v>
       </c>
       <c r="I2" t="n">
-        <v>9.3215</v>
+        <v>8.5547</v>
       </c>
       <c r="J2" t="n">
-        <v>7.9861</v>
+        <v>7.2715</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -558,10 +558,10 @@
         <v>0.863</v>
       </c>
       <c r="I3" t="n">
-        <v>7.5289</v>
+        <v>7.0266</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4261</v>
+        <v>6.9104</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
         <v>0.6935</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6423</v>
+        <v>7.0762</v>
       </c>
       <c r="J4" t="n">
-        <v>6.596</v>
+        <v>7.0058</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -648,14 +648,104 @@
         <v>0.5444</v>
       </c>
       <c r="I5" t="n">
-        <v>14.4231</v>
+        <v>15.401</v>
       </c>
       <c r="J5" t="n">
-        <v>13.2994</v>
+        <v>14.2865</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>supporting sentiment pipeline; refreshed after 5,000/1,000 split expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sentiment classification</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GoEmotions 7-class test split</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G6" t="n">
+        <v>571</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.0093</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.805</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 1; refreshed after 5,000/1,000 split expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sentiment classification</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GoEmotions 7-class test split</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15.5996</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14.1876</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 2; refreshed after 5,000/1,000 split expansion</t>
         </is>
       </c>
     </row>
@@ -670,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,10 +846,10 @@
         <v>0.409</v>
       </c>
       <c r="H2" t="n">
-        <v>11.3912</v>
+        <v>10.85</v>
       </c>
       <c r="I2" t="n">
-        <v>10.0558</v>
+        <v>9.566800000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -798,10 +888,10 @@
         <v>0.405</v>
       </c>
       <c r="H3" t="n">
-        <v>10.5252</v>
+        <v>10.479</v>
       </c>
       <c r="I3" t="n">
-        <v>10.4224</v>
+        <v>10.3628</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -840,10 +930,10 @@
         <v>0.83</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4056</v>
+        <v>9.5802</v>
       </c>
       <c r="I4" t="n">
-        <v>9.3592</v>
+        <v>9.5097</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -882,10 +972,10 @@
         <v>0.443</v>
       </c>
       <c r="H5" t="n">
-        <v>20.326</v>
+        <v>20.0711</v>
       </c>
       <c r="I5" t="n">
-        <v>19.3954</v>
+        <v>19.1839</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -924,10 +1014,10 @@
         <v>0.456</v>
       </c>
       <c r="H6" t="n">
-        <v>70.4072</v>
+        <v>69.8172</v>
       </c>
       <c r="I6" t="n">
-        <v>69.0069</v>
+        <v>68.48520000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -966,10 +1056,10 @@
         <v>0.842</v>
       </c>
       <c r="H7" t="n">
-        <v>19.1538</v>
+        <v>18.7908</v>
       </c>
       <c r="I7" t="n">
-        <v>19.0029</v>
+        <v>18.6446</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1008,10 +1098,10 @@
         <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>9.626300000000001</v>
+        <v>9.4666</v>
       </c>
       <c r="I8" t="n">
-        <v>9.532400000000001</v>
+        <v>9.357900000000001</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1050,14 +1140,98 @@
         <v>0.597</v>
       </c>
       <c r="H9" t="n">
-        <v>19.1336</v>
+        <v>19.7111</v>
       </c>
       <c r="I9" t="n">
-        <v>18.01</v>
+        <v>18.5965</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>supporting sentiment pipeline; refreshed on current YouTube-domain validation split</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sentiment classification</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>YouTube-domain validation comments</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>584</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.9434</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.7391</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 1; refreshed on current YouTube-domain validation split</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sentiment classification</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>YouTube-domain validation comments</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16.0515</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.6395</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 2; refreshed on current YouTube-domain validation split</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,306 +2533,306 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pre-tuning public baseline</t>
+          <t>alternative sentiment model 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-distilroberta-base</t>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4467</v>
+        <v>0.46</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+          <t>negative:16; neutral:23; positive:11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>anger:4; disgust:8; fear:4; joy:28; neutral:90; sadness:4; surprise:12</t>
+          <t>negative:23; neutral:4; positive:23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GoEmotions fine-tuned DistilBERT</t>
+          <t>alternative sentiment model 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert</t>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3267</v>
+        <v>0.74</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+          <t>negative:2; neutral:9; positive:39</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>anger:1; fear:1; joy:11; neutral:132; sadness:2; surprise:3</t>
+          <t>negative:5; positive:45</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted DistilBERT</t>
+          <t>alternative sentiment model 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5467</v>
+        <v>0.68</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+          <t>negative:36; neutral:5; positive:9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>anger:15; disgust:2; fear:4; joy:50; neutral:73; sadness:4; surprise:2</t>
+          <t>negative:31; neutral:1; positive:18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>public GoEmotions RoBERTa</t>
+          <t>alternative sentiment model 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SamLowe/roberta-base-go_emotions</t>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5333</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>neu</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+          <t>negative:16; neutral:23; positive:11</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>anger:1; disgust:3; fear:2; joy:51; neutral:88; sadness:5</t>
+          <t>neg:16; neu:22; pos:12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>public RoBERTa-large seven-emotion</t>
+          <t>alternative sentiment model 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-roberta-large</t>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4133</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>neu</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+          <t>negative:2; neutral:9; positive:39</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>anger:17; disgust:6; fear:2; joy:22; neutral:78; sadness:6; surprise:19</t>
+          <t>neg:1; neu:28; pos:21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted RoBERTa</t>
+          <t>alternative sentiment model 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5933</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>joy</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>neu</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+          <t>negative:36; neutral:5; positive:9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>anger:14; disgust:2; fear:6; joy:50; neutral:69; sadness:6; surprise:3</t>
+          <t>neg:19; neu:28; pos:3</t>
         </is>
       </c>
     </row>
@@ -2675,22 +2849,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted DistilRoBERTa</t>
+          <t>pre-tuning public baseline</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>150</v>
       </c>
       <c r="F32" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5467</v>
+        <v>0.4467</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2709,7 +2883,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>anger:13; disgust:4; fear:5; joy:53; neutral:65; sadness:6; surprise:4</t>
+          <t>anger:4; disgust:8; fear:4; joy:28; neutral:90; sadness:4; surprise:12</t>
         </is>
       </c>
     </row>
@@ -2721,46 +2895,454 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3-sentiment</t>
+          <t>7-emotion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>supporting sentiment pipeline</t>
+          <t>GoEmotions fine-tuned DistilBERT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>150</v>
       </c>
       <c r="F33" t="n">
+        <v>49</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>joy</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>anger:1; fear:1; joy:11; neutral:132; sadness:2; surprise:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted DistilBERT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>150</v>
+      </c>
+      <c r="F34" t="n">
+        <v>82</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>joy</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>anger:15; disgust:2; fear:4; joy:50; neutral:73; sadness:4; surprise:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>public GoEmotions RoBERTa</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SamLowe/roberta-base-go_emotions</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>150</v>
+      </c>
+      <c r="F35" t="n">
+        <v>80</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>joy</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>anger:1; disgust:3; fear:2; joy:51; neutral:88; sadness:5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>public RoBERTa-large seven-emotion</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-roberta-large</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>150</v>
+      </c>
+      <c r="F36" t="n">
+        <v>62</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>joy</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>anger:17; disgust:6; fear:2; joy:22; neutral:78; sadness:6; surprise:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted RoBERTa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>150</v>
+      </c>
+      <c r="F37" t="n">
+        <v>89</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>joy</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>anger:14; disgust:2; fear:6; joy:50; neutral:69; sadness:6; surprise:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted DistilRoBERTa</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>150</v>
+      </c>
+      <c r="F38" t="n">
+        <v>82</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>joy</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>anger:30; disgust:5; fear:10; joy:57; neutral:34; sadness:7; surprise:7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>anger:13; disgust:4; fear:5; joy:53; neutral:65; sadness:6; surprise:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>supporting sentiment pipeline</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>150</v>
+      </c>
+      <c r="F39" t="n">
         <v>105</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G39" t="n">
         <v>0.7</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>positive</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>negative:54; neutral:37; positive:59</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>negative:41; neutral:57; positive:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>150</v>
+      </c>
+      <c r="F40" t="n">
+        <v>94</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6267</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>negative:54; neutral:37; positive:59</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>negative:59; neutral:5; positive:86</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>150</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>negative:54; neutral:37; positive:59</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>neg:36; neu:78; pos:36</t>
         </is>
       </c>
     </row>
@@ -2775,7 +3357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2856,10 +3438,10 @@
         <v>0.58</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3355</v>
+        <v>1.2833</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1386</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="3">
@@ -2893,10 +3475,10 @@
         <v>0.52</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3355</v>
+        <v>1.2833</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1386</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="4">
@@ -2930,10 +3512,10 @@
         <v>0.24</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3355</v>
+        <v>1.2833</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1386</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="5">
@@ -2967,10 +3549,10 @@
         <v>0.48</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1028</v>
+        <v>0.1162</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8515</v>
+        <v>0.8977000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -3004,10 +3586,10 @@
         <v>0.34</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1028</v>
+        <v>0.1162</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8515</v>
+        <v>0.8977000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -3041,10 +3623,10 @@
         <v>0.16</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1028</v>
+        <v>0.1162</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8515</v>
+        <v>0.8977000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3078,10 +3660,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0463</v>
+        <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8547</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="9">
@@ -3115,10 +3697,10 @@
         <v>0.74</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0463</v>
+        <v>0.0704</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8547</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="10">
@@ -3152,10 +3734,10 @@
         <v>0.34</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0463</v>
+        <v>0.0704</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8547</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="11">
@@ -3189,10 +3771,10 @@
         <v>0.52</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9306</v>
+        <v>0.8872</v>
       </c>
       <c r="I11" t="n">
-        <v>1.945</v>
+        <v>2.0221</v>
       </c>
     </row>
     <row r="12">
@@ -3226,10 +3808,10 @@
         <v>0.74</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9306</v>
+        <v>0.8872</v>
       </c>
       <c r="I12" t="n">
-        <v>1.945</v>
+        <v>2.0221</v>
       </c>
     </row>
     <row r="13">
@@ -3263,10 +3845,10 @@
         <v>0.34</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9306</v>
+        <v>0.8872</v>
       </c>
       <c r="I13" t="n">
-        <v>1.945</v>
+        <v>2.0221</v>
       </c>
     </row>
     <row r="14">
@@ -3300,10 +3882,10 @@
         <v>0.48</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4004</v>
+        <v>1.332</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8108</v>
+        <v>6.463</v>
       </c>
     </row>
     <row r="15">
@@ -3337,10 +3919,10 @@
         <v>0.48</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4004</v>
+        <v>1.332</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8108</v>
+        <v>6.463</v>
       </c>
     </row>
     <row r="16">
@@ -3374,10 +3956,10 @@
         <v>0.28</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4004</v>
+        <v>1.332</v>
       </c>
       <c r="I16" t="n">
-        <v>6.8108</v>
+        <v>6.463</v>
       </c>
     </row>
     <row r="17">
@@ -3411,10 +3993,10 @@
         <v>0.62</v>
       </c>
       <c r="H17" t="n">
-        <v>0.151</v>
+        <v>0.1461</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9588</v>
+        <v>1.8465</v>
       </c>
     </row>
     <row r="18">
@@ -3448,10 +4030,10 @@
         <v>0.78</v>
       </c>
       <c r="H18" t="n">
-        <v>0.151</v>
+        <v>0.1461</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9588</v>
+        <v>1.8465</v>
       </c>
     </row>
     <row r="19">
@@ -3485,10 +4067,10 @@
         <v>0.38</v>
       </c>
       <c r="H19" t="n">
-        <v>0.151</v>
+        <v>0.1461</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9588</v>
+        <v>1.8465</v>
       </c>
     </row>
     <row r="20">
@@ -3522,10 +4104,10 @@
         <v>0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1088</v>
       </c>
       <c r="I20" t="n">
-        <v>0.979</v>
+        <v>1.0414</v>
       </c>
     </row>
     <row r="21">
@@ -3559,10 +4141,10 @@
         <v>0.78</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1088</v>
       </c>
       <c r="I21" t="n">
-        <v>0.979</v>
+        <v>1.0414</v>
       </c>
     </row>
     <row r="22">
@@ -3596,10 +4178,10 @@
         <v>0.36</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1088</v>
       </c>
       <c r="I22" t="n">
-        <v>0.979</v>
+        <v>1.0414</v>
       </c>
     </row>
     <row r="23">
@@ -3610,7 +4192,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3-sentiment pipeline</t>
+          <t>CardiffNLP Twitter RoBERTa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3633,10 +4215,10 @@
         <v>0.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1237</v>
+        <v>1.1145</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8761</v>
+        <v>1.9316</v>
       </c>
     </row>
     <row r="24">
@@ -3647,7 +4229,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3-sentiment pipeline</t>
+          <t>CardiffNLP Twitter RoBERTa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3670,10 +4252,10 @@
         <v>0.92</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1237</v>
+        <v>1.1145</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8761</v>
+        <v>1.9316</v>
       </c>
     </row>
     <row r="25">
@@ -3684,7 +4266,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3-sentiment pipeline</t>
+          <t>CardiffNLP Twitter RoBERTa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3707,232 +4289,232 @@
         <v>0.58</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1237</v>
+        <v>1.1145</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8761</v>
+        <v>1.9316</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pre-tuning baseline</t>
+          <t>lxyuan DistilBERT Multilingual</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-distilroberta-base</t>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4467</v>
+        <v>0.46</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3355</v>
+        <v>1.2043</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1386</v>
+        <v>0.8794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GoEmotions fine-tuned</t>
+          <t>lxyuan DistilBERT Multilingual</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert</t>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F27" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3267</v>
+        <v>0.74</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1028</v>
+        <v>1.2043</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8515</v>
+        <v>0.8794</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted (your model)</t>
+          <t>lxyuan DistilBERT Multilingual</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5467</v>
+        <v>0.68</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0463</v>
+        <v>1.2043</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8547</v>
+        <v>0.8794</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+          <t>FiniteAutomata BERTweet</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SamLowe/roberta-base-go_emotions</t>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5333</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9306</v>
+        <v>1.412</v>
       </c>
       <c r="I29" t="n">
-        <v>1.945</v>
+        <v>1.7399</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Public RoBERTa-large 7-emotion</t>
+          <t>FiniteAutomata BERTweet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-roberta-large</t>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4133</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4004</v>
+        <v>1.412</v>
       </c>
       <c r="I30" t="n">
-        <v>6.8108</v>
+        <v>1.7399</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted RoBERTa (SamLowe)</t>
+          <t>FiniteAutomata BERTweet</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5933</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.151</v>
+        <v>1.412</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9588</v>
+        <v>1.7399</v>
       </c>
     </row>
     <row r="32">
@@ -3943,12 +4525,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted DistilRoBERTa (j-hartmann)</t>
+          <t>Pre-tuning baseline</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3957,19 +4539,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F32" t="n">
         <v>150</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5467</v>
+        <v>0.4467</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09379999999999999</v>
+        <v>1.2833</v>
       </c>
       <c r="I32" t="n">
-        <v>0.979</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="33">
@@ -3980,33 +4562,329 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3-sentiment pipeline</t>
+          <t>GoEmotions fine-tuned</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3-sentiment</t>
+          <t>7-emotion</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
         <v>150</v>
       </c>
       <c r="G33" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8977000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted (your model)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>82</v>
+      </c>
+      <c r="F34" t="n">
+        <v>150</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0704</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8952</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SamLowe/roberta-base-go_emotions</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>80</v>
+      </c>
+      <c r="F35" t="n">
+        <v>150</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8872</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.0221</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Public RoBERTa-large 7-emotion</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>j-hartmann/emotion-english-roberta-large</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>62</v>
+      </c>
+      <c r="F36" t="n">
+        <v>150</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6.463</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted RoBERTa (SamLowe)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>89</v>
+      </c>
+      <c r="F37" t="n">
+        <v>150</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.5933</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1461</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.8465</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted DistilRoBERTa (j-hartmann)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>82</v>
+      </c>
+      <c r="F38" t="n">
+        <v>150</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.0414</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CardiffNLP Twitter RoBERTa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105</v>
+      </c>
+      <c r="F39" t="n">
+        <v>150</v>
+      </c>
+      <c r="G39" t="n">
         <v>0.7</v>
       </c>
-      <c r="H33" t="n">
-        <v>1.1237</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.8761</v>
+      <c r="H39" t="n">
+        <v>1.1145</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.9316</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>lxyuan DistilBERT Multilingual</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>94</v>
+      </c>
+      <c r="F40" t="n">
+        <v>150</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6267</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.2043</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8794</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FiniteAutomata BERTweet</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>150</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.7399</v>
       </c>
     </row>
   </sheetData>
@@ -4020,7 +4898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4080,10 +4958,10 @@
         <v>150</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4741</v>
+        <v>2.2592</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1386</v>
+        <v>0.9759</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4111,10 +4989,10 @@
         <v>150</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9543</v>
+        <v>1.0139</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8515</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4142,10 +5020,10 @@
         <v>150</v>
       </c>
       <c r="E4" t="n">
-        <v>0.901</v>
+        <v>0.9656</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8547</v>
+        <v>0.8952</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4173,10 +5051,10 @@
         <v>150</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8756</v>
+        <v>2.9093</v>
       </c>
       <c r="F5" t="n">
-        <v>1.945</v>
+        <v>2.0221</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4204,10 +5082,10 @@
         <v>150</v>
       </c>
       <c r="E6" t="n">
-        <v>8.2112</v>
+        <v>7.795</v>
       </c>
       <c r="F6" t="n">
-        <v>6.8108</v>
+        <v>6.463</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4235,10 +5113,10 @@
         <v>150</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1098</v>
+        <v>1.9926</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9588</v>
+        <v>1.8465</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4266,10 +5144,10 @@
         <v>150</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0728</v>
+        <v>1.1502</v>
       </c>
       <c r="F8" t="n">
-        <v>0.979</v>
+        <v>1.0414</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4297,14 +5175,76 @@
         <v>150</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9998</v>
+        <v>3.0461</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8761</v>
+        <v>1.9316</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>supporting sentiment pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>150</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.0837</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8794</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>150 reviewed Streamlit app comments</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>150</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.1519</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.7399</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 2</t>
         </is>
       </c>
     </row>
@@ -4319,7 +5259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4391,7 +5331,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.3355</v>
+        <v>1.2832</v>
       </c>
     </row>
     <row r="3">
@@ -4426,7 +5366,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.1028</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="4">
@@ -4461,7 +5401,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.0464</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="5">
@@ -4496,7 +5436,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9306</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="6">
@@ -4531,7 +5471,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.4004</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="7">
@@ -4566,7 +5506,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.1509</v>
+        <v>0.1462</v>
       </c>
     </row>
     <row r="8">
@@ -4601,7 +5541,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="9">
@@ -4636,7 +5576,77 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.1237</v>
+        <v>1.1145</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cf991100d706c13c0a080c097134c05b7f436c45</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-03-03 02:06:53+00:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1.2043</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>924fc4c80bccb8003d21fe84dd92c7887717f245</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2023-02-17 02:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>alternative sentiment model 2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1.412</v>
       </c>
     </row>
   </sheetData>
@@ -4650,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI151"/>
+  <dimension ref="A1:AO151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4829,6 +5839,36 @@
           <t>jhartmann_distilroberta_adapted_7_match</t>
         </is>
       </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>lxyuan_sentiment_3</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>lxyuan_sentiment_3_score</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>lxyuan_sentiment_3_match</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>bertweet_sentiment_3</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>bertweet_sentiment_3_score</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>bertweet_sentiment_3_match</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4988,6 +6028,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.9122</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5147,6 +6213,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5306,6 +6398,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5465,6 +6583,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.8834</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5624,6 +6768,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5783,6 +6953,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5942,6 +7138,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6101,6 +7323,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.5281</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6260,6 +7508,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.8254</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6419,6 +7693,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.5276999999999999</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.8157</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6578,6 +7878,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6737,6 +8063,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.5286</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6896,6 +8248,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.9608</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7055,6 +8433,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7214,6 +8618,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.7222</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.9391</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7373,6 +8803,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7532,6 +8988,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7691,6 +9173,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.7726</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7850,6 +9358,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.7184</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.8862</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8009,6 +9543,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.5066000000000001</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.9334</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8168,6 +9728,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.6859</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8327,6 +9913,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8486,6 +10098,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.6539</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.9015</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8645,6 +10283,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.9635</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>0.8206</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8804,6 +10468,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.6397</v>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.7992</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8963,6 +10653,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9122,6 +10838,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9281,6 +11023,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.7477</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9440,6 +11208,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.5673</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.9847</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9599,6 +11393,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.7266</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9758,6 +11578,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.7803</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9917,6 +11763,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10076,6 +11948,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.7786</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.8776</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10235,6 +12133,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.6383</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10394,6 +12318,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.6252</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10553,6 +12503,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.8875999999999999</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10712,6 +12688,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10871,6 +12873,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.5967</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.6081</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11030,6 +13058,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.5118</v>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11189,6 +13243,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.4903</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>0.9051</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11348,6 +13428,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN42" t="n">
+        <v>0.5427</v>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -11507,6 +13613,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.7039</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11666,6 +13798,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.8783</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11825,6 +13983,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -11984,6 +14168,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.6542</v>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12143,6 +14353,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.4848</v>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>0.8133</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12302,6 +14538,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN48" t="n">
+        <v>0.9096</v>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12461,6 +14723,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.5522</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12620,6 +14908,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN50" t="n">
+        <v>0.8372000000000001</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12779,6 +15093,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>0.5407</v>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN51" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12938,6 +15278,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN52" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13097,6 +15463,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN53" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -13256,6 +15648,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13415,6 +15833,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.9048</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -13574,6 +16018,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK56" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN56" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -13733,6 +16203,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>0.4538</v>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN57" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13892,6 +16388,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN58" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -14051,6 +16573,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN59" t="n">
+        <v>0.9907</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -14210,6 +16758,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK60" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN60" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -14369,6 +16943,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK61" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN61" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -14528,6 +17128,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN62" t="n">
+        <v>0.9598</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -14687,6 +17313,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN63" t="n">
+        <v>0.5881</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -14846,6 +17498,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN64" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15005,6 +17683,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>0.7688</v>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN65" t="n">
+        <v>0.9902</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -15164,6 +17868,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>0.5685</v>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN66" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -15323,6 +18053,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN67" t="n">
+        <v>0.9707</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -15482,6 +18238,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK68" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN68" t="n">
+        <v>0.9738</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -15641,6 +18423,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN69" t="n">
+        <v>0.9892</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -15800,6 +18608,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN70" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15959,6 +18793,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN71" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -16118,6 +18978,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>0.9493</v>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN72" t="n">
+        <v>0.9664</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -16277,6 +19163,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN73" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -16436,6 +19348,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN74" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -16595,6 +19533,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN75" t="n">
+        <v>0.9437</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -16754,6 +19718,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK76" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN76" t="n">
+        <v>0.9443</v>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -16913,6 +19903,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK77" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN77" t="n">
+        <v>0.5473</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17072,6 +20088,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK78" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN78" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17231,6 +20273,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK79" t="n">
+        <v>0.7161999999999999</v>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN79" t="n">
+        <v>0.9087</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -17390,6 +20458,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK80" t="n">
+        <v>0.8793</v>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN80" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17549,6 +20643,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK81" t="n">
+        <v>0.9251</v>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN81" t="n">
+        <v>0.9873</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -17708,6 +20828,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK82" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN82" t="n">
+        <v>0.9486</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -17867,6 +21013,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK83" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN83" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18026,6 +21198,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK84" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN84" t="n">
+        <v>0.4853</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18185,6 +21383,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK85" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN85" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -18344,6 +21568,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK86" t="n">
+        <v>0.9316</v>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN86" t="n">
+        <v>0.9905</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18503,6 +21753,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK87" t="n">
+        <v>0.8963</v>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN87" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18662,6 +21938,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK88" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN88" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18821,6 +22123,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK89" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN89" t="n">
+        <v>0.9656</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18980,6 +22308,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK90" t="n">
+        <v>0.6738</v>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN90" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19139,6 +22493,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK91" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN91" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19298,6 +22678,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK92" t="n">
+        <v>0.4974</v>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN92" t="n">
+        <v>0.9891</v>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19457,6 +22863,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK93" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN93" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19616,6 +23048,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK94" t="n">
+        <v>0.9656</v>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN94" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19775,6 +23233,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK95" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN95" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19934,6 +23418,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK96" t="n">
+        <v>0.6871</v>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN96" t="n">
+        <v>0.9666</v>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -20093,6 +23603,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK97" t="n">
+        <v>0.9383</v>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN97" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -20252,6 +23788,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK98" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN98" t="n">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -20411,6 +23973,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK99" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN99" t="n">
+        <v>0.9694</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -20570,6 +24158,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK100" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN100" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -20729,6 +24343,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK101" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN101" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -20888,6 +24528,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK102" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN102" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -21047,6 +24713,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK103" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN103" t="n">
+        <v>0.8735000000000001</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -21206,6 +24898,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK104" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN104" t="n">
+        <v>0.6563</v>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -21365,6 +25083,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK105" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN105" t="n">
+        <v>0.8528</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -21524,6 +25268,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK106" t="n">
+        <v>0.7108</v>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN106" t="n">
+        <v>0.6516</v>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -21683,6 +25453,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK107" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN107" t="n">
+        <v>0.7179</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -21842,6 +25638,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK108" t="n">
+        <v>0.6284</v>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN108" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -22001,6 +25823,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK109" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN109" t="n">
+        <v>0.8472</v>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -22160,6 +26008,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK110" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN110" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -22319,6 +26193,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK111" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN111" t="n">
+        <v>0.9025</v>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -22478,6 +26378,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK112" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN112" t="n">
+        <v>0.7363</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -22637,6 +26563,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK113" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN113" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -22796,6 +26748,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK114" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN114" t="n">
+        <v>0.9032</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -22955,6 +26933,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK115" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN115" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -23114,6 +27118,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK116" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN116" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -23273,6 +27303,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.6239</v>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.9318</v>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -23432,6 +27488,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.4792</v>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.9471000000000001</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -23591,6 +27673,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -23750,6 +27858,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -23909,6 +28043,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.7893</v>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -24068,6 +28228,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK122" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="AL122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>pos</t>
+        </is>
+      </c>
+      <c r="AN122" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -24227,6 +28413,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.6143999999999999</v>
+      </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.9529</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -24386,6 +28598,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.9297</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -24545,6 +28783,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="AL125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.9651</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -24704,6 +28968,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.9576</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -24863,6 +29153,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.8953</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -25022,6 +29338,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.8996</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -25181,6 +29523,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="AL129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -25340,6 +29708,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="AL130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.8603</v>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -25499,6 +29893,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="AL131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -25658,6 +30078,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -25817,6 +30263,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.9457</v>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -25976,6 +30448,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.6603</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -26135,6 +30633,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.7492</v>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -26294,6 +30818,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.6133</v>
+      </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.6166</v>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -26453,6 +31003,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.7169</v>
+      </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.9706</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -26612,6 +31188,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.7882</v>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -26771,6 +31373,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9401</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -26930,6 +31558,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.4705</v>
+      </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -27089,6 +31743,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.7822</v>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -27248,6 +31928,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.8024</v>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.5765</v>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -27407,6 +32113,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -27566,6 +32298,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK144" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN144" t="n">
+        <v>0.7055</v>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -27725,6 +32483,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK145" t="n">
+        <v>0.7452</v>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN145" t="n">
+        <v>0.8396</v>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -27884,6 +32668,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK146" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN146" t="n">
+        <v>0.6209</v>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -28043,6 +32853,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK147" t="n">
+        <v>0.9212</v>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN147" t="n">
+        <v>0.9598</v>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -28202,6 +33038,32 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="AK148" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN148" t="n">
+        <v>0.9137</v>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -28361,6 +33223,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK149" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN149" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -28520,6 +33408,32 @@
           <t>No</t>
         </is>
       </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK150" t="n">
+        <v>0.9313</v>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>neg</t>
+        </is>
+      </c>
+      <c r="AN150" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -28675,6 +33589,32 @@
         <v>0.749</v>
       </c>
       <c r="AI151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="AK151" t="n">
+        <v>0.8661</v>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>neu</t>
+        </is>
+      </c>
+      <c r="AN151" t="n">
+        <v>0.7889</v>
+      </c>
+      <c r="AO151" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/experiments/Experimental_results.xlsx
+++ b/experiments/Experimental_results.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Model_Selection" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="YouTube_Domain_Validation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Streamlit_App_Performance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="App_5Model_Comparison" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="App_Runtime" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Model_Revisions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Manual_Comment_Labels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Selection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YouTube_Domain_Validation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Streamlit_App_Performance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_5Model_Comparison" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App_Runtime" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Revisions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Comment_Labels" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1526,10 +1526,10 @@
         <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1577,10 +1577,10 @@
         <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1679,10 +1679,10 @@
         <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
         <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>0.74</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
         <v>150</v>
       </c>
       <c r="F36" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3267</v>
+        <v>0.4667</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3158,10 +3158,10 @@
         <v>150</v>
       </c>
       <c r="F37" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4733</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
         <v>150</v>
       </c>
       <c r="F38" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5333</v>
+        <v>0.2733</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3683,27 +3683,21 @@
       <c r="G2" t="n">
         <v>0.58</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.2324</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.0282</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pre-tuning baseline</t>
+          <t>GoEmotions fine-tuned</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-distilroberta-base</t>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3712,35 +3706,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
         <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.2324</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.0282</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pre-tuning baseline</t>
+          <t>YouTube-domain adapted</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-distilroberta-base</t>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3749,19 +3737,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.2324</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.0282</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3772,12 +3754,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GoEmotions fine-tuned</t>
+          <t>Public RoBERTa-large</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert</t>
+          <t>j-hartmann/emotion-english-roberta-large</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3793,28 +3775,22 @@
       </c>
       <c r="G5" t="n">
         <v>0.48</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0582</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8488</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GoEmotions fine-tuned</t>
+          <t>Public GoEmotions RoBERTa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert</t>
+          <t>SamLowe/roberta-base-go_emotions</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3823,72 +3799,60 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0582</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.8488</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GoEmotions fine-tuned</t>
+          <t>Sentiment pipeline</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert</t>
+          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0582</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8488</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted (your model)</t>
+          <t>Pre-tuning baseline</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3897,19 +3861,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9343</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="9">
@@ -3920,12 +3878,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted (your model)</t>
+          <t>GoEmotions fine-tuned</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3934,30 +3892,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
         <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9343</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted (your model)</t>
+          <t>YouTube-domain adapted</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3971,35 +3923,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9343</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+          <t>Public RoBERTa-large</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SamLowe/roberta-base-go_emotions</t>
+          <t>j-hartmann/emotion-english-roberta-large</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4008,19 +3954,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.9086</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.8941</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="12">
@@ -4031,7 +3971,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+          <t>Public GoEmotions RoBERTa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4045,72 +3985,60 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
         <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.9086</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.8941</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
+          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Public GoEmotions RoBERTa (SamLowe)</t>
+          <t>Sentiment pipeline</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SamLowe/roberta-base-go_emotions</t>
+          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
         <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.9086</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.8941</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Public RoBERTa-large 7-emotion</t>
+          <t>Pre-tuning baseline</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-roberta-large</t>
+          <t>j-hartmann/emotion-english-distilroberta-base</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4119,35 +4047,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.4107</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1657</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Public RoBERTa-large 7-emotion</t>
+          <t>GoEmotions fine-tuned</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-roberta-large</t>
+          <t>chase1zhang/youtube-emotion-distilbert</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4156,19 +4078,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.4107</v>
-      </c>
-      <c r="I15" t="n">
-        <v>7.1657</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="16">
@@ -4179,12 +4095,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Public RoBERTa-large 7-emotion</t>
+          <t>YouTube-domain adapted</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>j-hartmann/emotion-english-roberta-large</t>
+          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4193,35 +4109,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F16" t="n">
         <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.4107</v>
-      </c>
-      <c r="I16" t="n">
-        <v>7.1657</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted RoBERTa (SamLowe)</t>
+          <t>Public RoBERTa-large</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
+          <t>j-hartmann/emotion-english-roberta-large</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4230,35 +4140,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
         <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.1597</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.0179</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
+          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted RoBERTa (SamLowe)</t>
+          <t>Public GoEmotions RoBERTa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
+          <t>SamLowe/roberta-base-go_emotions</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4267,19 +4171,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.1597</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.0179</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19">
@@ -4290,995 +4188,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted RoBERTa (SamLowe)</t>
+          <t>Sentiment pipeline</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
+          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
         <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1597</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.0179</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted DistilRoBERTa (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>25</v>
-      </c>
-      <c r="F20" t="n">
-        <v>50</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.0381</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted DistilRoBERTa (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>36</v>
-      </c>
-      <c r="F21" t="n">
-        <v>50</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.0381</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted DistilRoBERTa (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>22</v>
-      </c>
-      <c r="F22" t="n">
-        <v>50</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.0381</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted RoBERTa-large (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-roberta-large-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>30</v>
-      </c>
-      <c r="F23" t="n">
-        <v>50</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7.3825</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted RoBERTa-large (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-roberta-large-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>43</v>
-      </c>
-      <c r="F24" t="n">
-        <v>50</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="I24" t="n">
-        <v>7.3825</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted RoBERTa-large (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-roberta-large-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>21</v>
-      </c>
-      <c r="F25" t="n">
-        <v>50</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7.3825</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CardiffNLP Twitter RoBERTa</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>30</v>
-      </c>
-      <c r="F26" t="n">
-        <v>50</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.2355</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.0197</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CardiffNLP Twitter RoBERTa</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>46</v>
-      </c>
-      <c r="F27" t="n">
-        <v>50</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.2355</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.0197</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CardiffNLP Twitter RoBERTa</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>29</v>
-      </c>
-      <c r="F28" t="n">
-        <v>50</v>
-      </c>
-      <c r="G28" t="n">
         <v>0.58</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.2355</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.0197</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>lxyuan DistilBERT Multilingual</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>23</v>
-      </c>
-      <c r="F29" t="n">
-        <v>50</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.1556</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.8353</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>lxyuan DistilBERT Multilingual</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>37</v>
-      </c>
-      <c r="F30" t="n">
-        <v>50</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.1556</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.8353</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>lxyuan DistilBERT Multilingual</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>34</v>
-      </c>
-      <c r="F31" t="n">
-        <v>50</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.1556</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.8353</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=d2dgJGkw5p0</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FiniteAutomata BERTweet</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>50</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.2548</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.7107</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=M8To7iorkxQ</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>FiniteAutomata BERTweet</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>50</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.2548</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.7107</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-_-eIVAX1yQ</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FiniteAutomata BERTweet</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>50</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.2548</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.7107</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Pre-tuning baseline</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>j-hartmann/emotion-english-distilroberta-base</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>67</v>
-      </c>
-      <c r="F35" t="n">
-        <v>150</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.4467</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.2324</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.0282</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GoEmotions fine-tuned</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-distilbert</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>49</v>
-      </c>
-      <c r="F36" t="n">
-        <v>150</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.3267</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.0582</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.8488</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted (your model)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-distilbert-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>84</v>
-      </c>
-      <c r="F37" t="n">
-        <v>150</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.9343</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Public GoEmotions RoBERTa (SamLowe)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>SamLowe/roberta-base-go_emotions</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>80</v>
-      </c>
-      <c r="F38" t="n">
-        <v>150</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.5333</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.9086</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1.8941</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Public RoBERTa-large 7-emotion</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>j-hartmann/emotion-english-roberta-large</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>62</v>
-      </c>
-      <c r="F39" t="n">
-        <v>150</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.4133</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.4107</v>
-      </c>
-      <c r="I39" t="n">
-        <v>7.1657</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted RoBERTa (SamLowe)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-samlowe-roberta-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>93</v>
-      </c>
-      <c r="F40" t="n">
-        <v>150</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.1597</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.0179</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted DistilRoBERTa (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-jhartmann-distilroberta-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>83</v>
-      </c>
-      <c r="F41" t="n">
-        <v>150</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.5533</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1.0381</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted RoBERTa-large (j-hartmann)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>chase1zhang/youtube-emotion-roberta-large-domain-adapted</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>94</v>
-      </c>
-      <c r="F42" t="n">
-        <v>150</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.6267</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="I42" t="n">
-        <v>7.3825</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CardiffNLP Twitter RoBERTa</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>cardiffnlp/twitter-roberta-base-sentiment-latest</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>105</v>
-      </c>
-      <c r="F43" t="n">
-        <v>150</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1.2355</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2.0197</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>lxyuan DistilBERT Multilingual</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>lxyuan/distilbert-base-multilingual-cased-sentiments-student</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>94</v>
-      </c>
-      <c r="F44" t="n">
-        <v>150</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.6267</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1.1556</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.8353</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>OVERALL</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>FiniteAutomata BERTweet</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>finiteautomata/bertweet-base-sentiment-analysis</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>3-sentiment</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>150</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.2548</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.7107</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/Experimental_results.xlsx
+++ b/experiments/Experimental_results.xlsx
@@ -423,11 +423,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G79"/>
+  <dimension ref="A2:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trades in-domain accuracy for YouTube-domain performance</t>
+          <t>Trades in-domain for YouTube-domain</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>App benchmark (150)</t>
+          <t>App benchmark (500)</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -984,12 +984,7 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>Runtime w/o loading</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>Purpose</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -1006,18 +1001,13 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>105/150</t>
+          <t>334/500</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.7</v>
+        <v>0.668</v>
       </c>
       <c r="F37" t="inlineStr">
-        <is>
-          <t>1.9316s</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>Best accuracy; recommended</t>
         </is>
@@ -1036,18 +1026,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>94/150</t>
+          <t>306/500</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6267</v>
+        <v>0.612</v>
       </c>
       <c r="F38" t="inlineStr">
-        <is>
-          <t>0.8794s</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>Fastest inference; multilingual</t>
         </is>
@@ -1066,655 +1051,532 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0/150*</t>
+          <t>228/500</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.7399s</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>*Label format mismatch; output correct</t>
+          <t>Label format: POS/NEU/NEG; output correct</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pipeline 3 - Business Decision Engine (rule-based, combining emotion + sentiment)</t>
+          <t>Experiment 2: Assessing the overall app performance on Streamlit Cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>Risk Level</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>App URL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://youtube-emotion-analyzer.streamlit.app/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Benchmark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Negative emotion ratio &gt;= 40% OR Negative sentiment ratio &gt;= 40%</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Review before scaling</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>500 comments across 10 YouTube videos (150 manually reviewed + 350 DeepSeek-labeled)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>Low Risk</t>
+          <t>Benchmark file</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dominant emotion is Joy/Surprise AND Positive sentiment ratio &gt;= 50%</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Scale positive creative</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Medium Risk (engagement)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Dominant emotion is Neutral</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Improve engagement hook</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>data/app_per_comment_manual_labels_500.csv</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Medium Risk (mixed)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>All other mixed signals</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Monitor and review samples</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Model / Pipeline</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Matched / 500</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pre-tuning baseline</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>179/500</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>GoEmotions fine-tuned</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>141/500</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>Experiment 2: Assessing the overall app performance on Streamlit Cloud</t>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted DistilBERT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>317/500</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Best project-owned 7-emotion</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>App URL</t>
+          <t>7-emotion</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://youtube-emotion-analyzer.streamlit.app/</t>
-        </is>
-      </c>
+          <t>Public GoEmotions RoBERTa</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>208/500</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>Benchmark</t>
+          <t>7-emotion</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>500 comments across 10 YouTube videos (150 manually reviewed + 350 DeepSeek-labeled)</t>
-        </is>
-      </c>
+          <t>Public RoBERTa-large</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>185/500</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>Benchmark file</t>
+          <t>7-emotion</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>data/app_per_comment_manual_labels_500.csv</t>
-        </is>
-      </c>
+          <t>YouTube-domain adapted RoBERTa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>315/500</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7-emotion</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>YouTube-domain adapted DistilRoBERTa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>306/500</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>Model / Pipeline</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>Matched / 500</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3-sentiment</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CardiffNLP sentiment pipeline</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>334/500</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Best overall signal</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pre-tuning baseline</t>
+          <t>lxyuan sentiment</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>179/500</t>
+          <t>306/500</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.358</v>
+        <v>0.612</v>
       </c>
       <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>3-sentiment</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GoEmotions fine-tuned</t>
+          <t>BERTweet sentiment</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>141/500</t>
+          <t>228/500</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.282</v>
+        <v>0.456</v>
       </c>
       <c r="F57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted DistilBERT</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>317/500</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Best project-owned 7-emotion</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Public GoEmotions RoBERTa</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>208/500</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Public RoBERTa-large</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>185/500</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>Per-video accuracy: YouTube-domain adapted DistilBERT (best project-owned model)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>7-emotion</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>YouTube-domain adapted RoBERTa</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>315/500</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="A61" s="1" t="n"/>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>Matched / 50</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Manual main label</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>7-emotion</t>
+          <t>rare_earths</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YouTube-domain adapted DistilRoBERTa</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>306/500</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>28/50</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>3-sentiment</t>
+          <t>avatar_clip</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CardiffNLP sentiment pipeline</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>334/500</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Best overall signal</t>
+          <t>37/50</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>joy</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>3-sentiment</t>
+          <t>shooting_news</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>lxyuan sentiment</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>306/500</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>17/50</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>anger</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>3-sentiment</t>
+          <t>anger_brand_crisis</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BERTweet sentiment</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>228/500</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>36/50</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>anger</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>fear_public_safety</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>25/50</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sadness_psa</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>37/50</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>sadness</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>Per-video accuracy: YouTube-domain adapted DistilBERT (best project-owned model)</t>
+          <t>surprise_product_fail</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>36/50</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>surprise</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n"/>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>Matched / 50</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>Manual main label</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>disgust_food_safety</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>36/50</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>disgust</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>rare_earths</t>
+          <t>joy_trailer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>28/50</t>
+          <t>33/50</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>joy</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>avatar_clip</t>
+          <t>brand_crisis_negative</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>37/50</t>
+          <t>32/50</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="E71" t="inlineStr">
-        <is>
-          <t>joy</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>shooting_news</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>17/50</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>anger</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>anger_brand_crisis</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>36/50</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>anger</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>fear_public_safety</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>25/50</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>fear</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>sadness_psa</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>37/50</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>sadness</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>surprise_product_fail</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>36/50</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>surprise</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>disgust_food_safety</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>36/50</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>disgust</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>joy_trailer</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>33/50</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>joy</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>brand_crisis_negative</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>32/50</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E79" t="inlineStr">
         <is>
           <t>anger</t>
         </is>
